--- a/cvs-review/cvs-metrics-v0_2026-10-12.xlsx
+++ b/cvs-review/cvs-metrics-v0_2026-10-12.xlsx
@@ -2486,7 +2486,7 @@
           <t>Kênh kế hoạch: So với 4 mốc kế hoạch E / HE / O / O+ do Finance cấp.
 Hàng ngành MCH2: target TÙY CHỌN DIO × MCH2 (CMC điền, chuỗi × tháng; T20) ⇒ có màu theo 4 mốc, áp xuống Region / Model / cửa hàng trong cùng ngành (chain plan); KHÔNG áp xuống ngành con MCH3 (ngành con chênh nhau tự nhiên); trống ⇒ số không màu
 Store không có SKU Core 1–3 ⇒ ⚪ unclassified range (KHÔNG đổi sang toàn danh mục)
-DIO âm hoặc mẫu (cogs_30d / 30) ≤ 0 ⇒ ⚪</t>
+Ô không màu ghi lý do: chưa có số tồn ⇒ ⚪ no stock data · tồn âm ⇒ ⚪ negative stock · không có giá vốn hàng bán trong kỳ ⇒ ⚪ no sales cost</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
